--- a/data/trans_dic/P37A$vacunapreferencia-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunapreferencia-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,55</t>
+          <t>0,84; 3,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,59</t>
+          <t>1,03; 3,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,07</t>
+          <t>0,22; 2,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,14</t>
+          <t>0,65; 3,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,41</t>
+          <t>0,48; 3,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,95</t>
+          <t>0,24; 2,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,27</t>
+          <t>1,8; 7,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,82</t>
+          <t>0,96; 2,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,83</t>
+          <t>1,0; 2,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,58</t>
+          <t>0,35; 1,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,87</t>
+          <t>0,98; 3,75</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,18</t>
+          <t>0,99; 3,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,37</t>
+          <t>0,62; 2,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,16</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,82</t>
+          <t>3,19; 8,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,62</t>
+          <t>0,46; 2,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,92</t>
+          <t>0,8; 2,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,28</t>
+          <t>0,44; 2,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,61</t>
+          <t>4,49; 9,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,26</t>
+          <t>0,88; 2,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,19</t>
+          <t>0,92; 2,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,78</t>
+          <t>0,55; 1,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,58</t>
+          <t>4,36; 8,07</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,62</t>
+          <t>1,16; 3,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,83</t>
+          <t>1,97; 4,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 9,97</t>
+          <t>5,06; 9,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,39</t>
+          <t>1,64; 4,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,7</t>
+          <t>0,85; 2,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,89</t>
+          <t>0,29; 2,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,55</t>
+          <t>3,74; 6,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,5</t>
+          <t>1,74; 3,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,33</t>
+          <t>1,62; 3,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,04</t>
+          <t>0,22; 1,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,62</t>
+          <t>4,79; 7,57</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,02</t>
+          <t>1,66; 5,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,19</t>
+          <t>1,51; 4,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,98</t>
+          <t>0,75; 3,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,23</t>
+          <t>5,55; 9,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,34</t>
+          <t>0,81; 3,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,34</t>
+          <t>0,84; 3,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,94</t>
+          <t>0,33; 2,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,13</t>
+          <t>7,26; 10,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,71</t>
+          <t>1,63; 3,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,19</t>
+          <t>1,36; 3,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,03</t>
+          <t>0,71; 2,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,46</t>
+          <t>6,92; 9,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,29</t>
+          <t>2,97; 7,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,15</t>
+          <t>2,37; 5,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,27</t>
+          <t>1,11; 4,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,71</t>
+          <t>10,04; 15,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,58</t>
+          <t>2,92; 7,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,68</t>
+          <t>0,92; 3,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,97</t>
+          <t>1,57; 5,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,53; 14,82</t>
+          <t>10,43; 14,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,55</t>
+          <t>3,44; 6,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,28</t>
+          <t>2,0; 4,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,02</t>
+          <t>1,65; 3,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 14,45</t>
+          <t>11,15; 14,53</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,54</t>
+          <t>2,89; 8,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,84</t>
+          <t>4,17; 9,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,57</t>
+          <t>1,81; 5,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,38; 16,1</t>
+          <t>10,24; 15,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,74</t>
+          <t>2,58; 6,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,73</t>
+          <t>2,51; 6,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,5</t>
+          <t>2,16; 6,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 12,02</t>
+          <t>9,15; 13,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,49</t>
+          <t>3,16; 6,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,17</t>
+          <t>3,75; 7,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,52</t>
+          <t>2,42; 5,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,12; 12,51</t>
+          <t>10,28; 14,14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,74</t>
+          <t>1,62; 6,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,83</t>
+          <t>2,16; 8,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,88</t>
+          <t>2,42; 6,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,61</t>
+          <t>5,31; 10,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,85</t>
+          <t>0,92; 4,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,28</t>
+          <t>0,8; 3,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,5</t>
+          <t>1,59; 5,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,25</t>
+          <t>3,98; 6,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,91</t>
+          <t>1,61; 4,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,7</t>
+          <t>1,67; 4,49</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,52</t>
+          <t>2,42; 5,32</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,89</t>
+          <t>4,88; 7,78</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,45</t>
+          <t>2,24; 3,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,69</t>
+          <t>2,45; 3,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,15</t>
+          <t>1,22; 2,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,33</t>
+          <t>6,96; 8,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,2</t>
+          <t>2,06; 3,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,49</t>
+          <t>1,49; 2,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,33</t>
+          <t>1,38; 2,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,0</t>
+          <t>7,14; 8,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,09</t>
+          <t>2,29; 3,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 2,85</t>
+          <t>2,1; 2,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,06</t>
+          <t>1,42; 2,05</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,96</t>
+          <t>7,29; 8,48</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>15297</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4021; 17540</t>
+          <t>4163; 18062</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3973; 16318</t>
+          <t>4681; 17100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>987; 8671</t>
+          <t>910; 8721</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7119</t>
+          <t>0; 9516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2854; 14677</t>
+          <t>3037; 14662</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1999; 14668</t>
+          <t>2080; 14228</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>940; 7720</t>
+          <t>937; 8398</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5082; 25894</t>
+          <t>6530; 25517</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8972; 27138</t>
+          <t>9259; 26869</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7996; 24985</t>
+          <t>8880; 25428</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2804; 12871</t>
+          <t>2891; 13382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7137; 27610</t>
+          <t>7514; 28880</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>33804</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50875</t>
+          <t>59128</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7295; 23416</t>
+          <t>7256; 22058</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4196; 16270</t>
+          <t>4269; 16810</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1963; 12755</t>
+          <t>1901; 12139</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11677; 37344</t>
+          <t>15224; 41212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2987; 16382</t>
+          <t>2900; 14800</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4903; 17802</t>
+          <t>4876; 17143</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1955; 12828</t>
+          <t>2486; 13926</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16331; 44070</t>
+          <t>22514; 48746</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12604; 30693</t>
+          <t>11939; 31571</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11838; 28439</t>
+          <t>11945; 28580</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6694; 20497</t>
+          <t>6381; 20473</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35210; 70948</t>
+          <t>42633; 78995</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40080</t>
+          <t>44704</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28225</t>
+          <t>31516</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68305</t>
+          <t>76220</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6808; 23092</t>
+          <t>7410; 21948</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13701; 32921</t>
+          <t>13453; 33801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6398</t>
+          <t>0; 7275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27536; 53455</t>
+          <t>31406; 60874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11090; 30256</t>
+          <t>11287; 30581</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5962; 19218</t>
+          <t>6063; 20055</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1973; 12520</t>
+          <t>1943; 13225</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19147; 38778</t>
+          <t>23319; 43291</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22579; 46532</t>
+          <t>23056; 47937</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23484; 46426</t>
+          <t>22613; 47763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3379; 13887</t>
+          <t>2990; 16212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52489; 85984</t>
+          <t>59575; 94219</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47260</t>
+          <t>52226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>58767</t>
+          <t>64334</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>106027</t>
+          <t>116560</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8603; 26056</t>
+          <t>8625; 27104</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9181; 25768</t>
+          <t>9290; 25090</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3936; 19238</t>
+          <t>4818; 19929</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19486; 73086</t>
+          <t>38877; 68551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4797; 17220</t>
+          <t>4176; 17305</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4381; 20581</t>
+          <t>5188; 19129</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2159; 12590</t>
+          <t>2133; 13233</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46432; 72192</t>
+          <t>53519; 76875</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16762; 38427</t>
+          <t>16839; 36128</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15897; 39264</t>
+          <t>16774; 38971</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8945; 26310</t>
+          <t>9199; 26269</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62191; 135461</t>
+          <t>99416; 136249</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72728</t>
+          <t>77045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67560</t>
+          <t>76235</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>140288</t>
+          <t>153280</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11467; 28182</t>
+          <t>11495; 28924</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10415; 26429</t>
+          <t>10179; 25708</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5362; 20393</t>
+          <t>5297; 19171</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59471; 88190</t>
+          <t>61206; 92835</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11645; 30633</t>
+          <t>11806; 28928</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4109; 16497</t>
+          <t>4129; 16812</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7292; 24688</t>
+          <t>7809; 25649</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57679; 81185</t>
+          <t>63515; 88565</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27143; 51793</t>
+          <t>27206; 52310</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17639; 37519</t>
+          <t>17502; 38268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16352; 39155</t>
+          <t>16094; 38415</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>122508; 160264</t>
+          <t>135779; 176999</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47897</t>
+          <t>52594</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>44630</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92526</t>
+          <t>102048</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7150; 22056</t>
+          <t>8459; 23804</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12550; 30478</t>
+          <t>12928; 29257</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5831; 18628</t>
+          <t>6048; 19508</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38217; 59258</t>
+          <t>41669; 65005</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8324; 23098</t>
+          <t>8832; 23197</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8816; 23815</t>
+          <t>8879; 23982</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9127; 24536</t>
+          <t>8159; 23632</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19414; 73149</t>
+          <t>40193; 59609</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19926; 41224</t>
+          <t>20069; 39553</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24317; 47574</t>
+          <t>24902; 47542</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17922; 39306</t>
+          <t>17250; 37828</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49955; 122146</t>
+          <t>86956; 119644</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>24656</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>44551</t>
+          <t>48292</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3650; 16240</t>
+          <t>3391; 14487</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6193; 22065</t>
+          <t>5392; 22431</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6194; 17685</t>
+          <t>6219; 17948</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14830; 30008</t>
+          <t>16468; 32189</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3447; 16195</t>
+          <t>3071; 16439</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2146; 12754</t>
+          <t>3114; 13603</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6236; 22023</t>
+          <t>6369; 22522</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16827; 30885</t>
+          <t>18488; 32255</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9194; 26721</t>
+          <t>8755; 25959</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9606; 30016</t>
+          <t>10693; 28714</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15507; 36301</t>
+          <t>15874; 34979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>36029; 55887</t>
+          <t>37844; 60304</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>251852</t>
+          <t>277278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>265094</t>
+          <t>293546</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>516946</t>
+          <t>570824</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>74819; 113119</t>
+          <t>73364; 111372</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>86116; 126484</t>
+          <t>83812; 125526</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42595; 73043</t>
+          <t>41274; 70793</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>199770; 288312</t>
+          <t>245821; 310395</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>67545; 108075</t>
+          <t>69680; 105793</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>53628; 88684</t>
+          <t>52958; 85022</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49125; 82588</t>
+          <t>48741; 82379</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>211722; 296987</t>
+          <t>266758; 325441</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>151285; 205842</t>
+          <t>152147; 207189</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>147335; 199000</t>
+          <t>146471; 200010</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>98108; 143223</t>
+          <t>98580; 142538</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>448678; 571131</t>
+          <t>530256; 616274</t>
         </is>
       </c>
     </row>
